--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-imagingstudy-pathology.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-imagingstudy-pathology.xlsx
@@ -373,7 +373,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -661,7 +661,7 @@
     <t>ImagingStudy.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|Appointment|AppointmentResponse|Task)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|Appointment|4.0.1|AppointmentResponse|4.0.1|Task|4.0.1)
 </t>
   </si>
   <si>
@@ -743,7 +743,7 @@
     <t>ImagingStudy.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -913,7 +913,7 @@
     <t>研究の理由。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1196,7 +1196,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1220,7 +1220,7 @@
     <t>適用される部位の側性を示すコード（左側、右側など）</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/bodysite-laterality</t>
+    <t>http://hl7.org/fhir/ValueSet/bodysite-laterality|4.0.1</t>
   </si>
   <si>
     <t>(0020,0060)</t>
@@ -1312,7 +1312,7 @@
     <t>パフォーマーの関与のタイプ</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/series-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/series-performer-function|4.0.1</t>
   </si>
   <si>
     <t>ImagingStudy.series.performer.actor</t>
